--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9602,0.0231,0.0131,0.0008</t>
-  </si>
-  <si>
-    <t>0.8613,0.0307,0.0496,0.0299</t>
-  </si>
-  <si>
-    <t>0.9470,0.0206,0.0085,0.0046</t>
-  </si>
-  <si>
-    <t>0.9355,0.0339,0.0169,0.0034</t>
-  </si>
-  <si>
-    <t>0.8253,0.0848,0.0116,0.0190</t>
-  </si>
-  <si>
-    <t>0.9702,0.0195,0.0036,0.0013</t>
-  </si>
-  <si>
-    <t>0.8289,0.1023,0.0140,0.0132</t>
-  </si>
-  <si>
-    <t>0.9150,0.0464,0.0108,0.0058</t>
-  </si>
-  <si>
-    <t>0.8795,0.0982,0.0033,0.0021</t>
-  </si>
-  <si>
-    <t>0.7494,0.2765,0.0126,0.0021</t>
-  </si>
-  <si>
-    <t>0.8987,0.0839,0.0130,0.0051</t>
-  </si>
-  <si>
-    <t>0.8573,0.0574,0.0145,0.0243</t>
-  </si>
-  <si>
-    <t>0.9909,0.0009,0.0105,0.0002</t>
-  </si>
-  <si>
-    <t>0.9679,0.0106,0.0222,0.0003</t>
-  </si>
-  <si>
-    <t>0.9803,0.0068,0.0071,0.0005</t>
-  </si>
-  <si>
-    <t>0.9469,0.0296,0.0196,0.0003</t>
-  </si>
-  <si>
-    <t>0.9788,0.0115,0.0053,0.0005</t>
-  </si>
-  <si>
-    <t>0.8231,0.2281,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.3507,0.7650,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.4703,0.6880,0.0060,0.0005</t>
-  </si>
-  <si>
-    <t>0.7561,0.3154,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.6708,0.4478,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.9650,0.0047,0.0370,0.0014</t>
-  </si>
-  <si>
-    <t>0.9854,0.0034,0.0091,0.0004</t>
-  </si>
-  <si>
-    <t>0.8889,0.0381,0.1013,0.0022</t>
-  </si>
-  <si>
-    <t>0.9691,0.0130,0.0149,0.0005</t>
-  </si>
-  <si>
-    <t>0.9519,0.0106,0.0380,0.0005</t>
-  </si>
-  <si>
-    <t>0.9326,0.0322,0.0207,0.0017</t>
-  </si>
-  <si>
-    <t>0.6346,0.0929,0.3844,0.0029</t>
-  </si>
-  <si>
-    <t>0.6572,0.5444,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9741,0.0267,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.7813,0.0240,0.3845,0.0016</t>
-  </si>
-  <si>
-    <t>0.9921,0.0062,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9040,0.0598,0.0101,0.0065</t>
-  </si>
-  <si>
-    <t>0.8995,0.0745,0.0213,0.0023</t>
-  </si>
-  <si>
-    <t>0.8572,0.1391,0.0072,0.0018</t>
-  </si>
-  <si>
-    <t>0.9632,0.0280,0.0100,0.0002</t>
-  </si>
-  <si>
-    <t>0.8738,0.0527,0.1179,0.0037</t>
-  </si>
-  <si>
-    <t>0.9781,0.0026,0.0248,0.0017</t>
-  </si>
-  <si>
-    <t>0.4961,0.2038,0.3246,0.0025</t>
-  </si>
-  <si>
-    <t>0.9443,0.0056,0.0676,0.0024</t>
-  </si>
-  <si>
-    <t>0.9263,0.0358,0.0294,0.0005</t>
-  </si>
-  <si>
-    <t>0.6417,0.2286,0.1506,0.0087</t>
-  </si>
-  <si>
-    <t>0.8735,0.0679,0.0575,0.0006</t>
-  </si>
-  <si>
-    <t>0.9674,0.0328,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9057,0.1261,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.4110,0.7005,0.0159,0.0008</t>
-  </si>
-  <si>
-    <t>0.9608,0.0479,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.4167,0.1664,0.6156,0.0037</t>
-  </si>
-  <si>
-    <t>0.4953,0.0647,0.5844,0.0005</t>
-  </si>
-  <si>
-    <t>0.9089,0.0172,0.1037,0.0006</t>
-  </si>
-  <si>
-    <t>0.9147,0.0228,0.0764,0.0017</t>
-  </si>
-  <si>
-    <t>0.7054,0.0195,0.3657,0.0006</t>
-  </si>
-  <si>
-    <t>0.7923,0.0711,0.1531,0.0015</t>
-  </si>
-  <si>
-    <t>0.8815,0.1199,0.0085,0.0026</t>
-  </si>
-  <si>
-    <t>0.8952,0.0736,0.0117,0.0047</t>
-  </si>
-  <si>
-    <t>0.8809,0.1007,0.0043,0.0028</t>
-  </si>
-  <si>
-    <t>0.4704,0.3642,0.3126,0.0106</t>
-  </si>
-  <si>
-    <t>0.9687,0.0265,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9345,0.0237,0.0052,0.0158</t>
-  </si>
-  <si>
-    <t>0.8500,0.1301,0.0158,0.0038</t>
-  </si>
-  <si>
-    <t>0.0029,0.9692,0.8988,0.0005</t>
-  </si>
-  <si>
-    <t>0.5003,0.0301,0.7397,0.0003</t>
-  </si>
-  <si>
-    <t>0.9625,0.0020,0.0612,0.0012</t>
-  </si>
-  <si>
-    <t>0.0092,0.9576,0.8090,0.0010</t>
-  </si>
-  <si>
-    <t>0.4758,0.1198,0.5361,0.0020</t>
-  </si>
-  <si>
-    <t>0.5446,0.5897,0.0121,0.0005</t>
-  </si>
-  <si>
-    <t>0.2455,0.8868,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9749,0.0236,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.9485,0.0386,0.0125,0.0007</t>
-  </si>
-  <si>
-    <t>0.2802,0.2206,0.6848,0.0090</t>
-  </si>
-  <si>
-    <t>0.5253,0.4805,0.0495,0.0004</t>
-  </si>
-  <si>
-    <t>0.2008,0.6045,0.3510,0.0032</t>
-  </si>
-  <si>
-    <t>0.1441,0.8768,0.0700,0.0005</t>
-  </si>
-  <si>
-    <t>0.1485,0.6470,0.4999,0.0013</t>
-  </si>
-  <si>
-    <t>0.9753,0.0030,0.0189,0.0021</t>
-  </si>
-  <si>
-    <t>0.9433,0.0067,0.0188,0.0131</t>
-  </si>
-  <si>
-    <t>0.9301,0.0081,0.0154,0.0185</t>
-  </si>
-  <si>
-    <t>0.9899,0.0022,0.0053,0.0005</t>
-  </si>
-  <si>
-    <t>0.9157,0.0127,0.0420,0.0163</t>
-  </si>
-  <si>
-    <t>0.9729,0.0068,0.0096,0.0036</t>
-  </si>
-  <si>
-    <t>0.1309,0.6040,0.5323,0.0012</t>
-  </si>
-  <si>
-    <t>0.1128,0.2795,0.8414,0.0005</t>
-  </si>
-  <si>
-    <t>0.7041,0.1019,0.2221,0.0019</t>
-  </si>
-  <si>
-    <t>0.6319,0.1673,0.2511,0.0023</t>
-  </si>
-  <si>
-    <t>0.1575,0.7213,0.3799,0.0017</t>
-  </si>
-  <si>
-    <t>0.0603,0.8385,0.5201,0.0014</t>
-  </si>
-  <si>
-    <t>0.8863,0.1016,0.0122,0.0030</t>
-  </si>
-  <si>
-    <t>0.6591,0.2712,0.0184,0.0116</t>
-  </si>
-  <si>
-    <t>0.9753,0.0148,0.0020,0.0015</t>
-  </si>
-  <si>
-    <t>0.8442,0.0768,0.0129,0.0155</t>
-  </si>
-  <si>
-    <t>0.7216,0.2339,0.0274,0.0088</t>
-  </si>
-  <si>
-    <t>0.7942,0.1210,0.0033,0.0040</t>
-  </si>
-  <si>
-    <t>0.5289,0.4472,0.0111,0.0036</t>
-  </si>
-  <si>
-    <t>0.8545,0.0680,0.0136,0.0190</t>
-  </si>
-  <si>
-    <t>0.9390,0.0489,0.0060,0.0025</t>
-  </si>
-  <si>
-    <t>0.8739,0.0687,0.0070,0.0117</t>
-  </si>
-  <si>
-    <t>0.9307,0.0335,0.0110,0.0075</t>
-  </si>
-  <si>
-    <t>0.9704,0.0099,0.0031,0.0061</t>
-  </si>
-  <si>
-    <t>0.9028,0.0493,0.0054,0.0066</t>
-  </si>
-  <si>
-    <t>0.9189,0.0346,0.0070,0.0107</t>
-  </si>
-  <si>
-    <t>0.8311,0.0866,0.0116,0.0134</t>
-  </si>
-  <si>
-    <t>0.8822,0.0356,0.0060,0.0271</t>
-  </si>
-  <si>
-    <t>0.8659,0.0126,0.2543,0.0031</t>
-  </si>
-  <si>
-    <t>0.9352,0.0292,0.0331,0.0006</t>
-  </si>
-  <si>
-    <t>0.9898,0.0016,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.9383,0.0126,0.0643,0.0021</t>
-  </si>
-  <si>
-    <t>0.2011,0.8593,0.0084,0.0009</t>
-  </si>
-  <si>
-    <t>0.1364,0.8814,0.0072,0.0040</t>
-  </si>
-  <si>
-    <t>0.4255,0.6334,0.0209,0.0028</t>
-  </si>
-  <si>
-    <t>0.8703,0.1567,0.0133,0.0012</t>
-  </si>
-  <si>
-    <t>0.1095,0.9027,0.0095,0.0041</t>
-  </si>
-  <si>
-    <t>0.5476,0.5253,0.0143,0.0015</t>
-  </si>
-  <si>
-    <t>0.9188,0.0891,0.0058,0.0004</t>
-  </si>
-  <si>
-    <t>0.9444,0.0209,0.0252,0.0015</t>
-  </si>
-  <si>
-    <t>0.9625,0.0084,0.0227,0.0022</t>
-  </si>
-  <si>
-    <t>0.8579,0.0893,0.0183,0.0033</t>
-  </si>
-  <si>
-    <t>0.9825,0.0024,0.0168,0.0003</t>
-  </si>
-  <si>
-    <t>0.9614,0.0157,0.0090,0.0011</t>
-  </si>
-  <si>
-    <t>0.7215,0.3658,0.0062,0.0008</t>
-  </si>
-  <si>
-    <t>0.3905,0.7544,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.6329,0.4004,0.0244,0.0005</t>
-  </si>
-  <si>
-    <t>0.1683,0.6448,0.2931,0.0012</t>
-  </si>
-  <si>
-    <t>0.9775,0.0216,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.8074,0.2907,0.0051,0.0004</t>
-  </si>
-  <si>
-    <t>0.7548,0.2735,0.0234,0.0038</t>
-  </si>
-  <si>
-    <t>0.9852,0.0109,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.7362,0.2091,0.0062,0.0061</t>
-  </si>
-  <si>
-    <t>0.9525,0.0303,0.0031,0.0017</t>
-  </si>
-  <si>
-    <t>0.8541,0.1405,0.0141,0.0030</t>
-  </si>
-  <si>
-    <t>0.9111,0.0608,0.0235,0.0111</t>
-  </si>
-  <si>
-    <t>0.9499,0.0379,0.0067,0.0020</t>
-  </si>
-  <si>
-    <t>0.8991,0.0400,0.0041,0.0068</t>
-  </si>
-  <si>
-    <t>0.8859,0.0845,0.0075,0.0055</t>
-  </si>
-  <si>
-    <t>0.0606,0.8817,0.4410,0.0011</t>
-  </si>
-  <si>
-    <t>0.0817,0.5964,0.7217,0.0029</t>
-  </si>
-  <si>
-    <t>0.3129,0.3875,0.4216,0.0026</t>
-  </si>
-  <si>
-    <t>0.7474,0.0563,0.2875,0.0016</t>
-  </si>
-  <si>
-    <t>0.9746,0.0068,0.0192,0.0005</t>
-  </si>
-  <si>
-    <t>0.9555,0.0118,0.0306,0.0030</t>
-  </si>
-  <si>
-    <t>0.9839,0.0034,0.0132,0.0006</t>
-  </si>
-  <si>
-    <t>0.9860,0.0046,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.9800,0.0027,0.0053,0.0039</t>
-  </si>
-  <si>
-    <t>0.9719,0.0063,0.0061,0.0039</t>
-  </si>
-  <si>
-    <t>0.9440,0.0072,0.0189,0.0136</t>
-  </si>
-  <si>
-    <t>0.9633,0.0038,0.0209,0.0066</t>
-  </si>
-  <si>
-    <t>0.7508,0.1121,0.1748,0.0055</t>
-  </si>
-  <si>
-    <t>0.9719,0.0139,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.5014,0.4425,0.0662,0.0202</t>
-  </si>
-  <si>
-    <t>0.8998,0.0593,0.0130,0.0097</t>
-  </si>
-  <si>
-    <t>0.8835,0.0760,0.0171,0.0060</t>
-  </si>
-  <si>
-    <t>0.9663,0.0142,0.0057,0.0015</t>
-  </si>
-  <si>
-    <t>0.9461,0.0185,0.0090,0.0076</t>
-  </si>
-  <si>
-    <t>0.7801,0.1526,0.0164,0.0064</t>
-  </si>
-  <si>
-    <t>0.1719,0.4905,0.7244,0.0220</t>
-  </si>
-  <si>
-    <t>0.9347,0.0322,0.0111,0.0033</t>
-  </si>
-  <si>
-    <t>0.9769,0.0103,0.0049,0.0014</t>
-  </si>
-  <si>
-    <t>0.8641,0.1472,0.0117,0.0008</t>
-  </si>
-  <si>
-    <t>0.9779,0.0101,0.0041,0.0012</t>
-  </si>
-  <si>
-    <t>0.9301,0.0438,0.0154,0.0021</t>
-  </si>
-  <si>
-    <t>0.9491,0.0392,0.0052,0.0008</t>
-  </si>
-  <si>
-    <t>0.9801,0.0066,0.0091,0.0002</t>
-  </si>
-  <si>
-    <t>0.9805,0.0073,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.8118,0.0882,0.0095,0.0143</t>
-  </si>
-  <si>
-    <t>0.8447,0.0709,0.0262,0.0150</t>
-  </si>
-  <si>
-    <t>0.8788,0.0577,0.0202,0.0178</t>
-  </si>
-  <si>
-    <t>0.8657,0.0761,0.0132,0.0123</t>
-  </si>
-  <si>
-    <t>0.8954,0.0538,0.0310,0.0121</t>
-  </si>
-  <si>
-    <t>0.7313,0.1970,0.0122,0.0106</t>
-  </si>
-  <si>
-    <t>0.9617,0.0271,0.0083,0.0020</t>
-  </si>
-  <si>
-    <t>0.8085,0.2201,0.0102,0.0044</t>
-  </si>
-  <si>
-    <t>0.9450,0.0573,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.8604,0.1144,0.0203,0.0038</t>
-  </si>
-  <si>
-    <t>0.7143,0.2592,0.0121,0.0032</t>
-  </si>
-  <si>
-    <t>0.9212,0.0672,0.0081,0.0010</t>
-  </si>
-  <si>
-    <t>0.9254,0.0434,0.0032,0.0039</t>
-  </si>
-  <si>
-    <t>0.9826,0.0187,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.8800,0.0589,0.0213,0.0108</t>
-  </si>
-  <si>
-    <t>0.8033,0.1799,0.0086,0.0056</t>
-  </si>
-  <si>
-    <t>0.0138,0.6380,0.8778,0.0010</t>
-  </si>
-  <si>
-    <t>0.8639,0.1307,0.0187,0.0033</t>
-  </si>
-  <si>
-    <t>0.9090,0.0201,0.0894,0.0007</t>
-  </si>
-  <si>
-    <t>0.7814,0.0354,0.2780,0.0014</t>
-  </si>
-  <si>
-    <t>0.9417,0.0061,0.0900,0.0005</t>
-  </si>
-  <si>
-    <t>0.8499,0.0179,0.2236,0.0002</t>
-  </si>
-  <si>
-    <t>0.8577,0.1202,0.0175,0.0002</t>
-  </si>
-  <si>
-    <t>0.8489,0.0073,0.2893,0.0006</t>
-  </si>
-  <si>
-    <t>0.8502,0.0219,0.2066,0.0013</t>
-  </si>
-  <si>
-    <t>0.9552,0.0187,0.0221,0.0004</t>
-  </si>
-  <si>
-    <t>0.9744,0.0068,0.0141,0.0006</t>
-  </si>
-  <si>
-    <t>0.9587,0.0159,0.0202,0.0003</t>
-  </si>
-  <si>
-    <t>0.9926,0.0027,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9834,0.0079,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.9714,0.0181,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.9886,0.0028,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.9941,0.0013,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.9021,0.1118,0.0050,0.0011</t>
-  </si>
-  <si>
-    <t>0.9026,0.0937,0.0070,0.0023</t>
-  </si>
-  <si>
-    <t>0.5625,0.5283,0.0110,0.0015</t>
-  </si>
-  <si>
-    <t>0.8424,0.1616,0.0107,0.0022</t>
-  </si>
-  <si>
-    <t>0.8886,0.0435,0.0111,0.0210</t>
-  </si>
-  <si>
-    <t>0.9867,0.0067,0.0024,0.0003</t>
-  </si>
-  <si>
-    <t>0.9880,0.0050,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9785,0.0072,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.9765,0.0082,0.0140,0.0004</t>
-  </si>
-  <si>
-    <t>0.9419,0.0202,0.0431,0.0021</t>
-  </si>
-  <si>
-    <t>0.9288,0.0224,0.0335,0.0004</t>
-  </si>
-  <si>
-    <t>0.9354,0.0214,0.0434,0.0021</t>
-  </si>
-  <si>
-    <t>0.8603,0.0339,0.1512,0.0044</t>
-  </si>
-  <si>
-    <t>0.7978,0.1336,0.0598,0.0005</t>
-  </si>
-  <si>
-    <t>0.7076,0.1113,0.1925,0.0019</t>
-  </si>
-  <si>
-    <t>0.7322,0.1306,0.0124,0.0174</t>
-  </si>
-  <si>
-    <t>0.9415,0.0363,0.0074,0.0048</t>
-  </si>
-  <si>
-    <t>0.9618,0.0305,0.0042,0.0006</t>
-  </si>
-  <si>
-    <t>0.9122,0.0733,0.0101,0.0035</t>
-  </si>
-  <si>
-    <t>0.9322,0.0456,0.0037,0.0025</t>
-  </si>
-  <si>
-    <t>0.9155,0.0743,0.0056,0.0028</t>
-  </si>
-  <si>
-    <t>0.8020,0.1278,0.0173,0.0134</t>
-  </si>
-  <si>
-    <t>0.9479,0.0225,0.0014,0.0016</t>
-  </si>
-  <si>
-    <t>0.9730,0.0204,0.0071,0.0002</t>
-  </si>
-  <si>
-    <t>0.9724,0.0340,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9628,0.0405,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.1033,0.1061,0.8635,0.0010</t>
-  </si>
-  <si>
-    <t>0.6677,0.0541,0.4700,0.0046</t>
-  </si>
-  <si>
-    <t>0.8819,0.0392,0.0785,0.0014</t>
-  </si>
-  <si>
-    <t>0.8926,0.0151,0.1520,0.0002</t>
-  </si>
-  <si>
-    <t>0.9359,0.0345,0.0263,0.0003</t>
-  </si>
-  <si>
-    <t>0.3291,0.2497,0.5900,0.0055</t>
-  </si>
-  <si>
-    <t>0.3667,0.2899,0.4257,0.0044</t>
-  </si>
-  <si>
-    <t>0.8619,0.0612,0.0873,0.0035</t>
-  </si>
-  <si>
-    <t>0.9745,0.0114,0.0107,0.0003</t>
-  </si>
-  <si>
-    <t>0.9940,0.0004,0.0041,0.0002</t>
-  </si>
-  <si>
-    <t>0.9833,0.0070,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.6889,0.2862,0.0089,0.0063</t>
-  </si>
-  <si>
-    <t>0.9303,0.0258,0.0034,0.0063</t>
-  </si>
-  <si>
-    <t>0.9094,0.0462,0.0052,0.0065</t>
-  </si>
-  <si>
-    <t>0.8735,0.1051,0.0098,0.0055</t>
-  </si>
-  <si>
-    <t>0.7110,0.2206,0.0172,0.0097</t>
-  </si>
-  <si>
-    <t>0.9382,0.0259,0.0041,0.0041</t>
-  </si>
-  <si>
-    <t>0.8247,0.1122,0.0217,0.0098</t>
-  </si>
-  <si>
-    <t>0.9405,0.0336,0.0031,0.0038</t>
-  </si>
-  <si>
-    <t>0.8883,0.0610,0.0486,0.0015</t>
-  </si>
-  <si>
-    <t>0.6770,0.0369,0.3733,0.0004</t>
-  </si>
-  <si>
-    <t>0.4770,0.1226,0.5180,0.0035</t>
-  </si>
-  <si>
-    <t>0.8935,0.0636,0.0267,0.0004</t>
-  </si>
-  <si>
-    <t>0.9355,0.0075,0.1058,0.0023</t>
-  </si>
-  <si>
-    <t>0.9359,0.0228,0.0338,0.0050</t>
-  </si>
-  <si>
-    <t>0.9813,0.0047,0.0096,0.0007</t>
-  </si>
-  <si>
-    <t>0.8660,0.0213,0.1419,0.0139</t>
-  </si>
-  <si>
-    <t>0.9646,0.0074,0.0114,0.0043</t>
-  </si>
-  <si>
-    <t>0.9539,0.0067,0.0391,0.0038</t>
-  </si>
-  <si>
-    <t>0.9700,0.0043,0.0057,0.0070</t>
-  </si>
-  <si>
-    <t>0.8877,0.0132,0.0859,0.0187</t>
-  </si>
-  <si>
-    <t>0.9664,0.0031,0.0130,0.0079</t>
-  </si>
-  <si>
-    <t>0.9421,0.0314,0.0117,0.0031</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9358,0.0327,0.0044,0.0203</t>
+  </si>
+  <si>
+    <t>0.0102,0.0013,0.0013,0.9948</t>
+  </si>
+  <si>
+    <t>0.2570,0.0071,0.0134,0.8233</t>
+  </si>
+  <si>
+    <t>0.1461,0.0070,0.0023,0.9290</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9860,0.0031,0.0012,0.0057</t>
+  </si>
+  <si>
+    <t>0.9930,0.0008,0.0003,0.0035</t>
+  </si>
+  <si>
+    <t>0.9961,0.0003,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9919,0.0026,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9901,0.0017,0.0004,0.0045</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9960,0.0012,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.7927,0.0041,0.3585,0.0022</t>
+  </si>
+  <si>
+    <t>0.2647,0.0092,0.8212,0.0034</t>
+  </si>
+  <si>
+    <t>0.6101,0.0107,0.5583,0.0005</t>
+  </si>
+  <si>
+    <t>0.1078,0.0360,0.8431,0.0116</t>
+  </si>
+  <si>
+    <t>0.9498,0.0048,0.0554,0.0023</t>
+  </si>
+  <si>
+    <t>0.0048,0.9926,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.0173,0.9816,0.0020,0.0018</t>
+  </si>
+  <si>
+    <t>0.1757,0.8936,0.0021,0.0014</t>
+  </si>
+  <si>
+    <t>0.0620,0.9501,0.0016,0.0034</t>
+  </si>
+  <si>
+    <t>0.0084,0.9863,0.0028,0.0021</t>
+  </si>
+  <si>
+    <t>0.4263,0.0062,0.6436,0.0175</t>
+  </si>
+  <si>
+    <t>0.0705,0.0050,0.9353,0.0032</t>
+  </si>
+  <si>
+    <t>0.0028,0.0137,0.9839,0.0136</t>
+  </si>
+  <si>
+    <t>0.3295,0.0042,0.7884,0.0014</t>
+  </si>
+  <si>
+    <t>0.0310,0.0242,0.9604,0.0066</t>
+  </si>
+  <si>
+    <t>0.1164,0.0239,0.8665,0.0254</t>
+  </si>
+  <si>
+    <t>0.0419,0.0011,0.9722,0.0034</t>
+  </si>
+  <si>
+    <t>0.6688,0.4750,0.0058,0.0010</t>
+  </si>
+  <si>
+    <t>0.5307,0.2276,0.3192,0.0184</t>
+  </si>
+  <si>
+    <t>0.0020,0.0019,0.9934,0.0056</t>
+  </si>
+  <si>
+    <t>0.0525,0.8964,0.0788,0.0079</t>
+  </si>
+  <si>
+    <t>0.7660,0.1711,0.0480,0.0432</t>
+  </si>
+  <si>
+    <t>0.9193,0.0188,0.0492,0.0103</t>
+  </si>
+  <si>
+    <t>0.8166,0.2576,0.0082,0.0006</t>
+  </si>
+  <si>
+    <t>0.0047,0.9898,0.0494,0.0004</t>
+  </si>
+  <si>
+    <t>0.0279,0.6700,0.4225,0.0213</t>
+  </si>
+  <si>
+    <t>0.2802,0.0031,0.7935,0.0114</t>
+  </si>
+  <si>
+    <t>0.0967,0.0125,0.9119,0.0068</t>
+  </si>
+  <si>
+    <t>0.0363,0.0046,0.7305,0.3654</t>
+  </si>
+  <si>
+    <t>0.0091,0.0485,0.9710,0.0057</t>
+  </si>
+  <si>
+    <t>0.0022,0.9725,0.0233,0.0103</t>
+  </si>
+  <si>
+    <t>0.0098,0.0174,0.9743,0.0044</t>
+  </si>
+  <si>
+    <t>0.0467,0.7960,0.0302,0.5395</t>
+  </si>
+  <si>
+    <t>0.0020,0.9937,0.0021,0.0111</t>
+  </si>
+  <si>
+    <t>0.0018,0.9851,0.0208,0.0040</t>
+  </si>
+  <si>
+    <t>0.0042,0.9891,0.0335,0.0015</t>
+  </si>
+  <si>
+    <t>0.0103,0.0042,0.9848,0.0037</t>
+  </si>
+  <si>
+    <t>0.0013,0.0712,0.9921,0.0031</t>
+  </si>
+  <si>
+    <t>0.0690,0.0198,0.9399,0.0022</t>
+  </si>
+  <si>
+    <t>0.0084,0.0052,0.9832,0.0041</t>
+  </si>
+  <si>
+    <t>0.0079,0.0063,0.9930,0.0004</t>
+  </si>
+  <si>
+    <t>0.0209,0.3024,0.9350,0.0039</t>
+  </si>
+  <si>
+    <t>0.9641,0.0543,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9843,0.0017,0.0022,0.0066</t>
+  </si>
+  <si>
+    <t>0.4682,0.6349,0.0047,0.0038</t>
+  </si>
+  <si>
+    <t>0.0102,0.2204,0.9637,0.0101</t>
+  </si>
+  <si>
+    <t>0.9913,0.0056,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9953,0.0026,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.9906,0.0045,0.0032,0.0006</t>
+  </si>
+  <si>
+    <t>0.0017,0.8717,0.9707,0.0009</t>
+  </si>
+  <si>
+    <t>0.0069,0.0540,0.9891,0.0019</t>
+  </si>
+  <si>
+    <t>0.0089,0.0173,0.9773,0.0099</t>
+  </si>
+  <si>
+    <t>0.0006,0.8878,0.9752,0.0001</t>
+  </si>
+  <si>
+    <t>0.0078,0.0031,0.9903,0.0027</t>
+  </si>
+  <si>
+    <t>0.0422,0.9505,0.0137,0.0035</t>
+  </si>
+  <si>
+    <t>0.0076,0.9941,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9750,0.0049,0.0211,0.0039</t>
+  </si>
+  <si>
+    <t>0.1734,0.1259,0.7636,0.0080</t>
+  </si>
+  <si>
+    <t>0.0135,0.1129,0.9616,0.0082</t>
+  </si>
+  <si>
+    <t>0.0065,0.5344,0.9360,0.0009</t>
+  </si>
+  <si>
+    <t>0.0080,0.7350,0.8486,0.0035</t>
+  </si>
+  <si>
+    <t>0.0005,0.9969,0.0232,0.0010</t>
+  </si>
+  <si>
+    <t>0.0050,0.9153,0.8532,0.0019</t>
+  </si>
+  <si>
+    <t>0.0751,0.0006,0.0089,0.9474</t>
+  </si>
+  <si>
+    <t>0.0023,0.0024,0.0036,0.9970</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0163,0.0013,0.0042,0.9898</t>
+  </si>
+  <si>
+    <t>0.0004,0.0041,0.0003,0.9989</t>
+  </si>
+  <si>
+    <t>0.0030,0.0141,0.0049,0.9947</t>
+  </si>
+  <si>
+    <t>0.0004,0.9600,0.9704,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9635,0.8989,0.0004</t>
+  </si>
+  <si>
+    <t>0.0056,0.7493,0.7406,0.0131</t>
+  </si>
+  <si>
+    <t>0.0046,0.4329,0.9383,0.0021</t>
+  </si>
+  <si>
+    <t>0.0013,0.9455,0.8924,0.0004</t>
+  </si>
+  <si>
+    <t>0.0032,0.9664,0.1070,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0041,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9952,0.0026,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9917,0.0022,0.0014,0.0024</t>
+  </si>
+  <si>
+    <t>0.9939,0.0028,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9921,0.0022,0.0010,0.0028</t>
+  </si>
+  <si>
+    <t>0.9948,0.0019,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9937,0.0015,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9915,0.0028,0.0013,0.0023</t>
+  </si>
+  <si>
+    <t>0.9860,0.0008,0.0007,0.0145</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9946,0.0018,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9968,0.0007,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9931,0.0011,0.0005,0.0038</t>
+  </si>
+  <si>
+    <t>0.9961,0.0006,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.0244,0.0023,0.9856,0.0009</t>
+  </si>
+  <si>
+    <t>0.0091,0.3254,0.9460,0.0084</t>
+  </si>
+  <si>
+    <t>0.8254,0.0201,0.0518,0.0971</t>
+  </si>
+  <si>
+    <t>0.0778,0.0126,0.9385,0.0045</t>
+  </si>
+  <si>
+    <t>0.1469,0.9051,0.0015,0.0027</t>
+  </si>
+  <si>
+    <t>0.0479,0.9637,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.0624,0.9542,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.0099,0.9808,0.0126,0.0052</t>
+  </si>
+  <si>
+    <t>0.0243,0.9773,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.0216,0.9729,0.0037,0.0022</t>
+  </si>
+  <si>
+    <t>0.6036,0.5425,0.0035,0.0006</t>
+  </si>
+  <si>
+    <t>0.8399,0.0127,0.1250,0.0191</t>
+  </si>
+  <si>
+    <t>0.1524,0.0288,0.8332,0.0102</t>
+  </si>
+  <si>
+    <t>0.6739,0.1275,0.1526,0.0517</t>
+  </si>
+  <si>
+    <t>0.1816,0.0105,0.8254,0.0173</t>
+  </si>
+  <si>
+    <t>0.5019,0.0364,0.2543,0.3036</t>
+  </si>
+  <si>
+    <t>0.0009,0.9958,0.0163,0.0009</t>
+  </si>
+  <si>
+    <t>0.0015,0.9890,0.0065,0.0065</t>
+  </si>
+  <si>
+    <t>0.0003,0.9981,0.0015,0.0110</t>
+  </si>
+  <si>
+    <t>0.0045,0.8253,0.7173,0.0007</t>
+  </si>
+  <si>
+    <t>0.0084,0.9913,0.0071,0.0001</t>
+  </si>
+  <si>
+    <t>0.9357,0.0601,0.0218,0.0034</t>
+  </si>
+  <si>
+    <t>0.8250,0.2013,0.0154,0.0011</t>
+  </si>
+  <si>
+    <t>0.9719,0.0321,0.0050,0.0022</t>
+  </si>
+  <si>
+    <t>0.9941,0.0003,0.0005,0.0033</t>
+  </si>
+  <si>
+    <t>0.9882,0.0005,0.0004,0.0094</t>
+  </si>
+  <si>
+    <t>0.9941,0.0010,0.0039,0.0005</t>
+  </si>
+  <si>
+    <t>0.9974,0.0001,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9951,0.0017,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.9906,0.0011,0.0005,0.0061</t>
+  </si>
+  <si>
+    <t>0.9899,0.0029,0.0017,0.0028</t>
+  </si>
+  <si>
+    <t>0.0044,0.7876,0.8251,0.0045</t>
+  </si>
+  <si>
+    <t>0.0008,0.8874,0.9720,0.0003</t>
+  </si>
+  <si>
+    <t>0.0633,0.0330,0.9088,0.0056</t>
+  </si>
+  <si>
+    <t>0.0105,0.1601,0.9684,0.0007</t>
+  </si>
+  <si>
+    <t>0.9710,0.0091,0.0082,0.0023</t>
+  </si>
+  <si>
+    <t>0.7657,0.0060,0.3026,0.0038</t>
+  </si>
+  <si>
+    <t>0.5353,0.0008,0.6982,0.0017</t>
+  </si>
+  <si>
+    <t>0.9402,0.0039,0.0599,0.0066</t>
+  </si>
+  <si>
+    <t>0.2667,0.0014,0.0040,0.8587</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.0009,0.9997</t>
+  </si>
+  <si>
+    <t>0.0013,0.0029,0.0008,0.9986</t>
+  </si>
+  <si>
+    <t>0.0008,0.0017,0.0003,0.9990</t>
+  </si>
+  <si>
+    <t>0.0011,0.9565,0.6394,0.0015</t>
+  </si>
+  <si>
+    <t>0.9879,0.0005,0.0005,0.0125</t>
+  </si>
+  <si>
+    <t>0.4015,0.7006,0.0061,0.0103</t>
+  </si>
+  <si>
+    <t>0.9929,0.0036,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9377,0.1455,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9869,0.0009,0.0020,0.0051</t>
+  </si>
+  <si>
+    <t>0.0759,0.0017,0.0031,0.9625</t>
+  </si>
+  <si>
+    <t>0.9840,0.0029,0.0020,0.0070</t>
+  </si>
+  <si>
+    <t>0.0050,0.0310,0.9653,0.0544</t>
+  </si>
+  <si>
+    <t>0.9747,0.0002,0.0005,0.0264</t>
+  </si>
+  <si>
+    <t>0.5250,0.0107,0.0174,0.5474</t>
+  </si>
+  <si>
+    <t>0.8201,0.2452,0.0054,0.0017</t>
+  </si>
+  <si>
+    <t>0.8122,0.1959,0.0114,0.0182</t>
+  </si>
+  <si>
+    <t>0.9953,0.0014,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.1110,0.8517,0.0284,0.0261</t>
+  </si>
+  <si>
+    <t>0.8443,0.0968,0.0733,0.0244</t>
+  </si>
+  <si>
+    <t>0.9835,0.0080,0.0043,0.0011</t>
+  </si>
+  <si>
+    <t>0.9867,0.0010,0.0011,0.0080</t>
+  </si>
+  <si>
+    <t>0.9966,0.0015,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9966,0.0008,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9924,0.0002,0.0004,0.0061</t>
+  </si>
+  <si>
+    <t>0.9949,0.0006,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9925,0.0034,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9867,0.0027,0.0007,0.0046</t>
+  </si>
+  <si>
+    <t>0.9888,0.0006,0.0006,0.0086</t>
+  </si>
+  <si>
+    <t>0.9363,0.1172,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9183,0.1122,0.0069,0.0013</t>
+  </si>
+  <si>
+    <t>0.6057,0.4434,0.0160,0.0096</t>
+  </si>
+  <si>
+    <t>0.0054,0.2464,0.9716,0.0066</t>
+  </si>
+  <si>
+    <t>0.9771,0.0065,0.0115,0.0044</t>
+  </si>
+  <si>
+    <t>0.9662,0.0253,0.0055,0.0043</t>
+  </si>
+  <si>
+    <t>0.9947,0.0020,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9875,0.0046,0.0003,0.0032</t>
+  </si>
+  <si>
+    <t>0.0002,0.0108,0.9969,0.0012</t>
+  </si>
+  <si>
+    <t>0.9472,0.0444,0.0109,0.0021</t>
+  </si>
+  <si>
+    <t>0.0024,0.0755,0.9852,0.0011</t>
+  </si>
+  <si>
+    <t>0.0602,0.0421,0.9321,0.0035</t>
+  </si>
+  <si>
+    <t>0.0264,0.0103,0.9653,0.0064</t>
+  </si>
+  <si>
+    <t>0.0338,0.1450,0.9647,0.0020</t>
+  </si>
+  <si>
+    <t>0.0170,0.0154,0.9804,0.0016</t>
+  </si>
+  <si>
+    <t>0.0271,0.0017,0.9778,0.0037</t>
+  </si>
+  <si>
+    <t>0.0127,0.0132,0.9817,0.0030</t>
+  </si>
+  <si>
+    <t>0.0323,0.0258,0.9336,0.0120</t>
+  </si>
+  <si>
+    <t>0.4397,0.0052,0.7187,0.0017</t>
+  </si>
+  <si>
+    <t>0.3314,0.1405,0.6371,0.0197</t>
+  </si>
+  <si>
+    <t>0.2320,0.2300,0.5071,0.0036</t>
+  </si>
+  <si>
+    <t>0.0235,0.5604,0.7025,0.0016</t>
+  </si>
+  <si>
+    <t>0.8008,0.0347,0.1729,0.0158</t>
+  </si>
+  <si>
+    <t>0.7102,0.0135,0.3999,0.0050</t>
+  </si>
+  <si>
+    <t>0.2000,0.0243,0.8021,0.0038</t>
+  </si>
+  <si>
+    <t>0.9646,0.0433,0.0058,0.0017</t>
+  </si>
+  <si>
+    <t>0.9597,0.0620,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.9901,0.0087,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9913,0.0097,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9724,0.0406,0.0048,0.0014</t>
+  </si>
+  <si>
+    <t>0.8982,0.0412,0.0566,0.0018</t>
+  </si>
+  <si>
+    <t>0.9622,0.0015,0.0513,0.0020</t>
+  </si>
+  <si>
+    <t>0.4041,0.0143,0.0363,0.5553</t>
+  </si>
+  <si>
+    <t>0.4591,0.0263,0.6782,0.0067</t>
+  </si>
+  <si>
+    <t>0.6761,0.0018,0.2784,0.0252</t>
+  </si>
+  <si>
+    <t>0.4374,0.0023,0.6679,0.0029</t>
+  </si>
+  <si>
+    <t>0.0195,0.4209,0.7685,0.0396</t>
+  </si>
+  <si>
+    <t>0.1888,0.3370,0.5723,0.1917</t>
+  </si>
+  <si>
+    <t>0.6653,0.0064,0.4957,0.0017</t>
+  </si>
+  <si>
+    <t>0.0122,0.0197,0.9346,0.0256</t>
+  </si>
+  <si>
+    <t>0.9929,0.0011,0.0005,0.0036</t>
+  </si>
+  <si>
+    <t>0.9960,0.0015,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9933,0.0022,0.0010,0.0017</t>
+  </si>
+  <si>
+    <t>0.9816,0.0224,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.9893,0.0027,0.0013,0.0047</t>
+  </si>
+  <si>
+    <t>0.9897,0.0052,0.0024,0.0026</t>
+  </si>
+  <si>
+    <t>0.9901,0.0049,0.0012,0.0023</t>
+  </si>
+  <si>
+    <t>0.9954,0.0005,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.0047,0.0211,0.9778,0.0184</t>
+  </si>
+  <si>
+    <t>0.1626,0.2182,0.7214,0.0110</t>
+  </si>
+  <si>
+    <t>0.9603,0.0098,0.0200,0.0075</t>
+  </si>
+  <si>
+    <t>0.0432,0.0024,0.9719,0.0016</t>
+  </si>
+  <si>
+    <t>0.0007,0.2253,0.9926,0.0015</t>
+  </si>
+  <si>
+    <t>0.0038,0.0684,0.9797,0.0075</t>
+  </si>
+  <si>
+    <t>0.0016,0.0026,0.9956,0.0012</t>
+  </si>
+  <si>
+    <t>0.0957,0.0275,0.8883,0.0063</t>
+  </si>
+  <si>
+    <t>0.0020,0.0041,0.9959,0.0016</t>
+  </si>
+  <si>
+    <t>0.0065,0.0491,0.9467,0.0276</t>
+  </si>
+  <si>
+    <t>0.0411,0.0297,0.9274,0.0065</t>
+  </si>
+  <si>
+    <t>0.5936,0.0859,0.2419,0.1408</t>
+  </si>
+  <si>
+    <t>0.6440,0.0021,0.5061,0.0045</t>
+  </si>
+  <si>
+    <t>0.8838,0.0109,0.0863,0.0219</t>
+  </si>
+  <si>
+    <t>0.9909,0.0013,0.0007,0.0042</t>
+  </si>
+  <si>
+    <t>0.9959,0.0023,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0011,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9927,0.0052,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9937,0.0017,0.0007,0.0024</t>
+  </si>
+  <si>
+    <t>0.9884,0.0122,0.0014,0.0008</t>
+  </si>
+  <si>
+    <t>0.9895,0.0056,0.0019,0.0018</t>
+  </si>
+  <si>
+    <t>0.9939,0.0014,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.0069,0.0167,0.9807,0.0016</t>
+  </si>
+  <si>
+    <t>0.0015,0.0686,0.9796,0.0017</t>
+  </si>
+  <si>
+    <t>0.0042,0.0087,0.9909,0.0020</t>
+  </si>
+  <si>
+    <t>0.0153,0.0280,0.9324,0.0315</t>
+  </si>
+  <si>
+    <t>0.0470,0.0061,0.9613,0.0043</t>
+  </si>
+  <si>
+    <t>0.0213,0.1147,0.9127,0.0743</t>
+  </si>
+  <si>
+    <t>0.0457,0.0178,0.9476,0.0037</t>
+  </si>
+  <si>
+    <t>0.2357,0.0203,0.5121,0.2115</t>
+  </si>
+  <si>
+    <t>0.2896,0.0009,0.0023,0.8551</t>
+  </si>
+  <si>
+    <t>0.0777,0.0021,0.0158,0.9440</t>
+  </si>
+  <si>
+    <t>0.0689,0.0019,0.0007,0.9759</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.0011,0.9991</t>
+  </si>
+  <si>
+    <t>0.0030,0.0001,0.0002,0.9988</t>
+  </si>
+  <si>
+    <t>0.9013,0.0120,0.0190,0.0987</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1984,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,10 +2194,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,10 +2236,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,10 +2250,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,10 +2390,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2614,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,10 +2740,10 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,10 +3398,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3538,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,10 +3622,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4084,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,10 +4140,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4728,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4798,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5078,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,10 +5106,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
